--- a/output/labour_force_simulation_確認用.xlsx
+++ b/output/labour_force_simulation_確認用.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF86E800-4465-46A3-B322-B3DCFEF7515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DF6D23-AB4E-4981-8BC4-C23F3DB63B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{69463FB7-C361-49B8-A8FD-E57D74F44FE4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="32">
   <si>
     <t>year</t>
   </si>
@@ -157,6 +157,59 @@
   </si>
   <si>
     <t>E/RY</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>D_C</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>MHS</t>
+  </si>
+  <si>
+    <t>MHD</t>
+  </si>
+  <si>
+    <t>MHD_RY</t>
+  </si>
+  <si>
+    <t>労働時間</t>
+    <rPh sb="0" eb="4">
+      <t>ロウドウジカン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレーの線は、労働投入量の付加価値額に対する比（資本集約的成長）</t>
+    <rPh sb="4" eb="5">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ロウドウトウニュウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>フカカチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ガク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シホン</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>シュウヤクテキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイチョウ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1000,7 +1053,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$K$2:$K$47</c:f>
+              <c:f>labour_force_simulation!$M$2:$M$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -1098,49 +1151,49 @@
                   <c:v>70040</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>70467.921958304098</c:v>
+                  <c:v>71599.808961890507</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>71066.777852032101</c:v>
+                  <c:v>74050.296155954595</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>71775.0099946962</c:v>
+                  <c:v>75906.3309958748</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>72345.791809096394</c:v>
+                  <c:v>77265.793065261096</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>72836.189322544495</c:v>
+                  <c:v>77912.030606500193</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>73212.7836881033</c:v>
+                  <c:v>77753.848194833903</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>73465.884722657502</c:v>
+                  <c:v>77105.056422016802</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>73628.867571187293</c:v>
+                  <c:v>76444.986549918598</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>73698.696748731105</c:v>
+                  <c:v>75890.209500555095</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>73697.707347292206</c:v>
+                  <c:v>75413.756387778005</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>73640.192229529799</c:v>
+                  <c:v>75010.347303944902</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>73561.307032192693</c:v>
+                  <c:v>74694.203553825893</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>73390.877554644394</c:v>
+                  <c:v>74344.277210815999</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>73192.002705167804</c:v>
+                  <c:v>74007.185566661705</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>72957.802629568701</c:v>
+                  <c:v>73662.511037226999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1316,7 +1369,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$L$2:$L$47</c:f>
+              <c:f>labour_force_simulation!$O$2:$O$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -1414,49 +1467,49 @@
                   <c:v>68280</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>69073.594231087205</c:v>
+                  <c:v>73629.847564697906</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>69839.201394407006</c:v>
+                  <c:v>76766.179229139394</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>70483.671680189902</c:v>
+                  <c:v>77935.886644214101</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>70983.1643471141</c:v>
+                  <c:v>77624.521647657399</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>71351.654539158699</c:v>
+                  <c:v>76589.128430508397</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>71604.7962080625</c:v>
+                  <c:v>75412.8411145133</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>71760.274108128302</c:v>
+                  <c:v>74430.598241660904</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>71835.867106205405</c:v>
+                  <c:v>73723.257438978893</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>71830.504075241406</c:v>
+                  <c:v>73218.942179816906</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>71758.349957732498</c:v>
+                  <c:v>72842.877826329801</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>71627.606961482394</c:v>
+                  <c:v>72521.374337719302</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>71447.950606554194</c:v>
+                  <c:v>72209.8143866194</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>71232.869334308503</c:v>
+                  <c:v>71898.452919464995</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>70989.752697937904</c:v>
+                  <c:v>71577.432067082394</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>70724.721823155007</c:v>
+                  <c:v>71245.804083346506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1633,7 +1686,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$N$2:$N$47</c:f>
+              <c:f>labour_force_simulation!$S$2:$S$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -1731,49 +1784,49 @@
                   <c:v>68280</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>68861.866972279196</c:v>
+                  <c:v>71036.567899467307</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>69565.393803957195</c:v>
+                  <c:v>73673.360705947503</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>70259.0352677685</c:v>
+                  <c:v>75467.0929886542</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>70788.9094711207</c:v>
+                  <c:v>76515.147327450104</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>71213.264054629093</c:v>
+                  <c:v>76549.806844729304</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>71512.051171833606</c:v>
+                  <c:v>75701.448928908401</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>71691.861812459101</c:v>
+                  <c:v>74651.760599983594</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>71790.755984546704</c:v>
+                  <c:v>73863.296931297999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>71804.595924219597</c:v>
+                  <c:v>73317.074990685098</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>71755.604513857907</c:v>
+                  <c:v>72915.266724324494</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>71645.858801675902</c:v>
+                  <c:v>72585.654395629797</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>71492.046212293106</c:v>
+                  <c:v>72288.278394379202</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>71278.695999278396</c:v>
+                  <c:v>71970.139968914504</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>71043.437348111707</c:v>
+                  <c:v>71651.590878967603</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>70782.651965030396</c:v>
+                  <c:v>71320.729629710797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1782,6 +1835,517 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-AEFB-4914-BFFC-8FD355994DB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1571244608"/>
+        <c:axId val="1571245088"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1571244608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1571245088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickLblSkip val="5"/>
+        <c:tickMarkSkip val="5"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1571245088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="80000"/>
+          <c:min val="50000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1571244608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>labour_force_simulation!$A$2:$A$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2040</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>labour_force_simulation!$K$2:$K$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>0.93293718169999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9423240034</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97076526230000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96869565219999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96481970100000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.95895196510000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.95410414829999901</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.93493761139999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.92780748660000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.92170818509999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.93375111909999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.93137254899999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.92908438059999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.93738656989999902</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.92803738319999995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.91988950279999904</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.9205909511</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.90725436179999996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.91457753019999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.92264678469999994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.92703461180000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.937911571</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.94439208289999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.9657794677</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.98347910589999998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.99602780540000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.0148809519999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.0257680870000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.065141004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.1051107979999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.1440817534510399</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.1842283705605401</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.2234654913804499</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.26025140924879</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.2905356238150401</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.3126670863688199</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.3297128546113199</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.34498988625422</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.3603043661377301</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.3766007478260101</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.39394173150578</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.41162338041476</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.4298278117635499</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.4483821657635101</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.4672201272368099</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D97F-4AE4-ACB7-0289D5231FB3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1958,516 +2522,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>labour_force_simulation!$A$2:$A$47</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
-                <c:pt idx="0">
-                  <c:v>1995</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2003</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2004</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2005</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2006</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2007</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2008</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2009</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2010</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2011</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2012</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2013</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2014</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2025</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2026</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2027</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2028</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2029</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2030</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2031</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2032</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2033</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2034</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2035</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2036</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2037</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2038</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2039</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2040</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>labour_force_simulation!$J$2:$J$47</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
-                <c:pt idx="0">
-                  <c:v>0.93293718169999995</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.9423240034</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.97076526230000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.96869565219999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.96481970100000003</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.95895196510000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.95410414829999901</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.93493761139999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.92780748660000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.92170818509999997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.93375111909999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.93137254899999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.92908438059999998</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.93738656989999902</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.92803738319999995</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.91988950279999904</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.9205909511</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.90725436179999996</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.91457753019999999</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.92264678469999994</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.92703461180000002</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.937911571</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.94439208289999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.9657794677</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.98347910589999998</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.99602780540000002</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.0148809519999999</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.0257680870000001</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.065141004</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.1051107979999999</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.1312078489858199</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.15674908041497</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.1812412259655001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.2058705857532499</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.23042167089837</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.25459443694746</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.2782309343712299</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.30149055090067</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.3244162675742801</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1.34723431359444</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1.3697056892894599</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1.3913050951294399</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.4125359573602101</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.43345264496608</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1.45416261100852</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D97F-4AE4-ACB7-0289D5231FB3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1571244608"/>
-        <c:axId val="1571245088"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1571244608"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1571245088"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:tickLblSkip val="5"/>
-        <c:tickMarkSkip val="5"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1571245088"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0.8"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1571244608"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -2652,7 +2706,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$G$2:$G$47</c:f>
+              <c:f>labour_force_simulation!$H$2:$H$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -2750,49 +2804,49 @@
                   <c:v>0.63888204763338097</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.64467479231399905</c:v>
+                  <c:v>0.65504006149607996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.65231465634782804</c:v>
+                  <c:v>0.679709723857712</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.66112044900899203</c:v>
+                  <c:v>0.69918509815293095</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.66895153064074597</c:v>
+                  <c:v>0.71445816826568798</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.67617640454346895</c:v>
+                  <c:v>0.723289583142251</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.68261595410904397</c:v>
+                  <c:v>0.72494380863208097</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.68826160753108101</c:v>
+                  <c:v>0.72236327920195598</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.69334534765563105</c:v>
+                  <c:v>0.71987519351663598</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.69794956398321095</c:v>
+                  <c:v>0.718718541358213</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.70224070138956596</c:v>
+                  <c:v>0.718582120552826</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.70607590566901501</c:v>
+                  <c:v>0.71919947173883103</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.710033093493183</c:v>
+                  <c:v>0.72097956152764797</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.71341140662142499</c:v>
+                  <c:v>0.72269422102260195</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.71653101118153395</c:v>
+                  <c:v>0.72453067273642102</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.71935391321216602</c:v>
+                  <c:v>0.72632581038106603</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2837,7 +2891,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$I$2:$I$47</c:f>
+              <c:f>labour_force_simulation!$J$2:$J$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -2935,49 +2989,49 @@
                   <c:v>2.51284980011422E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.2791292000568099E-2</c:v>
+                  <c:v>7.8665162741282397E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.1126384134101499E-2</c:v>
+                  <c:v>5.0902625590218201E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.1121205375515598E-2</c:v>
+                  <c:v>5.7865793466481503E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.1520012415980599E-2</c:v>
+                  <c:v>9.7151107628826398E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.2281853059728299E-2</c:v>
+                  <c:v>1.7484126022216901E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.32299938698564E-2</c:v>
+                  <c:v>2.63961117497701E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.4147574304665499E-2</c:v>
+                  <c:v>3.18175737866737E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2.4964550552993601E-2</c:v>
+                  <c:v>3.3771863076131899E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.5700601341285899E-2</c:v>
+                  <c:v>3.3906014053778001E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.6352282904573601E-2</c:v>
+                  <c:v>3.3130423189720003E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.7082132290445499E-2</c:v>
+                  <c:v>3.2324779120007703E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.8129745152489099E-2</c:v>
+                  <c:v>3.2210332863553202E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.8779892348246201E-2</c:v>
+                  <c:v>3.1934364432237697E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.9355192885087901E-2</c:v>
+                  <c:v>3.1829269950718102E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.9813818209167401E-2</c:v>
+                  <c:v>3.1790681237199699E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3116,7 +3170,6 @@
         <c:axId val="1693861760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="0.25"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -3408,7 +3461,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$P$2:$P$47</c:f>
+              <c:f>labour_force_simulation!$U$2:$U$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -3724,7 +3777,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$Q$2:$Q$47</c:f>
+              <c:f>labour_force_simulation!$V$2:$V$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -3822,49 +3875,49 @@
                   <c:v>105.74570233854732</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>106.97474714431966</c:v>
+                  <c:v>110.01481787125182</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>108.16044818709463</c:v>
+                  <c:v>114.09843689940762</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>109.15854372028791</c:v>
+                  <c:v>116.87640233646306</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>109.932111424987</c:v>
+                  <c:v>118.49953124895478</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>110.50279470211973</c:v>
+                  <c:v>118.55320868008255</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>110.89483693365727</c:v>
+                  <c:v>117.23935098173828</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>111.13562661937169</c:v>
+                  <c:v>115.6136914975741</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>111.25269801177855</c:v>
+                  <c:v>114.39259242883382</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>111.24439224909619</c:v>
+                  <c:v>113.54665477882158</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>111.13264667451215</c:v>
+                  <c:v>112.92437157243998</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>110.93016410327148</c:v>
+                  <c:v>112.41389870780516</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>110.65192907937771</c:v>
+                  <c:v>111.95335046365062</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>110.31883124408937</c:v>
+                  <c:v>111.46064731131253</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>109.94231484890491</c:v>
+                  <c:v>110.96730816008611</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>109.53185972302153</c:v>
+                  <c:v>110.45490108364689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4040,7 +4093,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>labour_force_simulation!$R$2:$R$47</c:f>
+              <c:f>labour_force_simulation!$W$2:$W$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="46"/>
@@ -4138,49 +4191,49 @@
                   <c:v>84.964467266575085</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>84.78821927279391</c:v>
+                  <c:v>87.197780316693169</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>85.306116505431646</c:v>
+                  <c:v>89.989406611851066</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>85.667951968170641</c:v>
+                  <c:v>91.724950519945395</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>85.848790078659647</c:v>
+                  <c:v>92.539306766183032</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>85.868095246613819</c:v>
+                  <c:v>92.123807747802914</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>85.746983725415134</c:v>
+                  <c:v>90.652739104738444</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>85.508598059515151</c:v>
+                  <c:v>88.954055303087273</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>85.175755302463799</c:v>
+                  <c:v>87.579677933754567</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>84.832425511443148</c:v>
+                  <c:v>86.58807818401462</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>84.411910310397133</c:v>
+                  <c:v>85.772832828761636</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>83.938109818315894</c:v>
+                  <c:v>85.060815073314345</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>83.42237788916718</c:v>
+                  <c:v>84.403541682832042</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>82.879563796379756</c:v>
+                  <c:v>83.737379425134662</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>82.318638010126492</c:v>
+                  <c:v>83.086095503284469</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>81.746241325422915</c:v>
+                  <c:v>82.435129124916457</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4309,6 +4362,515 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1527933471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>labour_force_simulation!$A$2:$A$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2040</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>labour_force_simulation!$L$2:$L$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>117.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>117.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>116.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>113.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>114.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>113.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>112.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>112.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>112.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>111.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>112.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>111.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>110.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>108.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>108.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>108.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>107.7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>107.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>106.9</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>106.1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>105.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>102.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>100.7</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>100.8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>100.9</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>99.891000000000005</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>98.492525999999998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>92.5419540954491</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>88.978807218882494</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>86.950272169451594</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>85.981280989656696</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>85.561245735490601</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>85.3792650584912</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>85.289684526502796</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>85.232011914010897</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>85.188465253239102</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>85.151029007410401</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>85.119492339868799</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>85.093301238008493</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>85.072031232417899</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>85.055506577126494</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>85.042778165112196</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D9A7-4DDF-9363-71CD510A07A9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1571244608"/>
+        <c:axId val="1571245088"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1571244608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1571245088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickLblSkip val="5"/>
+        <c:tickMarkSkip val="5"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1571245088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1571244608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4524,6 +5086,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -6588,17 +7190,533 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
@@ -6630,13 +7748,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>312420</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
@@ -6668,13 +7786,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
@@ -6706,16 +7824,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>41910</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>346710</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6735,6 +7853,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="グラフ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04638843-3B54-4AA8-9928-B3037C573E1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7040,10 +8196,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D408CA2-AA7C-4999-820F-D84672938E40}">
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AG69"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7060,47 +8216,62 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="4"/>
+      <c r="X1" s="4"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1995</v>
       </c>
@@ -7117,49 +8288,64 @@
         <v>1.1159999999999899</v>
       </c>
       <c r="F2">
+        <v>1.052</v>
+      </c>
+      <c r="G2">
         <v>0.95899999999999996</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.63151313047102897</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>3.1353135313531302E-2</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.93293718169999995</v>
       </c>
-      <c r="K2">
+      <c r="L2">
+        <v>117.8</v>
+      </c>
+      <c r="M2">
         <v>66660</v>
       </c>
-      <c r="L2">
+      <c r="N2">
+        <v>7852548</v>
+      </c>
+      <c r="O2">
         <v>64570</v>
       </c>
-      <c r="M2">
+      <c r="P2">
+        <v>7606346</v>
+      </c>
+      <c r="Q2">
         <v>0.135843768238777</v>
       </c>
-      <c r="N2">
+      <c r="R2">
+        <v>16.002395898527901</v>
+      </c>
+      <c r="S2">
         <v>64570</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>2090</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <f>D2/D$2*100</f>
         <v>100</v>
       </c>
-      <c r="Q2">
-        <f>L2/L$2*100</f>
+      <c r="V2">
+        <f>S2/S$2*100</f>
         <v>100</v>
       </c>
-      <c r="R2">
-        <f>Q2/P2*100</f>
+      <c r="W2">
+        <f>V2/U2*100</f>
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1996</v>
       </c>
@@ -7176,49 +8362,64 @@
         <v>1.115</v>
       </c>
       <c r="F3">
+        <v>1.054</v>
+      </c>
+      <c r="G3">
         <v>0.96</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.63208160266734403</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>3.3527045149754103E-2</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.9423240034</v>
       </c>
-      <c r="K3">
+      <c r="L3">
+        <v>117.9</v>
+      </c>
+      <c r="M3">
         <v>67110</v>
       </c>
-      <c r="L3">
+      <c r="N3">
+        <v>7912269</v>
+      </c>
+      <c r="O3">
         <v>64860</v>
       </c>
-      <c r="M3">
+      <c r="P3">
+        <v>7646994</v>
+      </c>
+      <c r="Q3">
         <v>0.13239693541834799</v>
       </c>
-      <c r="N3">
+      <c r="R3">
+        <v>15.609598685823199</v>
+      </c>
+      <c r="S3">
         <v>64860</v>
       </c>
-      <c r="O3">
+      <c r="T3">
         <v>2250</v>
       </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P47" si="0">D3/D$2*100</f>
+      <c r="U3">
+        <f t="shared" ref="U3:U47" si="0">D3/D$2*100</f>
         <v>103.06422584889465</v>
       </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q47" si="1">L3/L$2*100</f>
+      <c r="V3">
+        <f t="shared" ref="V3:V47" si="1">S3/S$2*100</f>
         <v>100.44912498064116</v>
       </c>
-      <c r="R3">
-        <f t="shared" ref="R3:R47" si="2">Q3/P3*100</f>
+      <c r="W3">
+        <f t="shared" ref="W3:W47" si="2">V3/U3*100</f>
         <v>97.462649288136532</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1997</v>
       </c>
@@ -7235,49 +8436,64 @@
         <v>1.1159999999999899</v>
       </c>
       <c r="F4">
+        <v>1.0669999999999999</v>
+      </c>
+      <c r="G4">
         <v>0.97699999999999998</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.63554044816510702</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>3.3888315898040297E-2</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.97076526230000004</v>
       </c>
-      <c r="K4">
+      <c r="L4">
+        <v>116.3</v>
+      </c>
+      <c r="M4">
         <v>67870</v>
       </c>
-      <c r="L4">
+      <c r="N4">
+        <v>7893281</v>
+      </c>
+      <c r="O4">
         <v>65570</v>
       </c>
-      <c r="M4">
+      <c r="P4">
+        <v>7625791</v>
+      </c>
+      <c r="Q4">
         <v>0.13206020878819</v>
       </c>
-      <c r="N4">
+      <c r="R4">
+        <v>15.358602282066499</v>
+      </c>
+      <c r="S4">
         <v>65570</v>
       </c>
-      <c r="O4">
+      <c r="T4">
         <v>2300</v>
       </c>
-      <c r="P4">
+      <c r="U4">
         <f t="shared" si="0"/>
         <v>104.45810378552184</v>
       </c>
-      <c r="Q4">
+      <c r="V4">
         <f t="shared" si="1"/>
         <v>101.54870682979711</v>
       </c>
-      <c r="R4">
+      <c r="W4">
         <f t="shared" si="2"/>
         <v>97.214771424820768</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1998</v>
       </c>
@@ -7294,49 +8510,64 @@
         <v>1.1140000000000001</v>
       </c>
       <c r="F5">
+        <v>1.0680000000000001</v>
+      </c>
+      <c r="G5">
         <v>0.98299999999999998</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.63241879474551499</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>4.1071691447077799E-2</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.96869565219999998</v>
       </c>
-      <c r="K5">
+      <c r="L5">
+        <v>115</v>
+      </c>
+      <c r="M5">
         <v>67930</v>
       </c>
-      <c r="L5">
+      <c r="N5">
+        <v>7811950</v>
+      </c>
+      <c r="O5">
         <v>65140</v>
       </c>
-      <c r="M5">
+      <c r="P5">
+        <v>7491100</v>
+      </c>
+      <c r="Q5">
         <v>0.13356419242265799</v>
       </c>
-      <c r="N5">
+      <c r="R5">
+        <v>15.359882128605699</v>
+      </c>
+      <c r="S5">
         <v>65140</v>
       </c>
-      <c r="O5">
+      <c r="T5">
         <v>2790</v>
       </c>
-      <c r="P5">
+      <c r="U5">
         <f t="shared" si="0"/>
         <v>102.60455600521566</v>
       </c>
-      <c r="Q5">
+      <c r="V5">
         <f t="shared" si="1"/>
         <v>100.88276289298437</v>
       </c>
-      <c r="R5">
+      <c r="W5">
         <f t="shared" si="2"/>
         <v>98.321913588180479</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1999</v>
       </c>
@@ -7353,49 +8584,64 @@
         <v>1.099</v>
       </c>
       <c r="F6">
+        <v>1.0609999999999999</v>
+      </c>
+      <c r="G6">
         <v>0.98</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.62812138058837097</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>4.6762059300781797E-2</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.96481970100000003</v>
       </c>
-      <c r="K6">
+      <c r="L6">
+        <v>113.7</v>
+      </c>
+      <c r="M6">
         <v>67790</v>
       </c>
-      <c r="L6">
+      <c r="N6">
+        <v>7707723</v>
+      </c>
+      <c r="O6">
         <v>64620</v>
       </c>
-      <c r="M6">
+      <c r="P6">
+        <v>7347294</v>
+      </c>
+      <c r="Q6">
         <v>0.13296468067921199</v>
       </c>
-      <c r="N6">
+      <c r="R6">
+        <v>15.1180841932264</v>
+      </c>
+      <c r="S6">
         <v>64620</v>
       </c>
-      <c r="O6">
+      <c r="T6">
         <v>3170</v>
       </c>
-      <c r="P6">
+      <c r="U6">
         <f t="shared" si="0"/>
         <v>102.24441455441335</v>
       </c>
-      <c r="Q6">
+      <c r="V6">
         <f t="shared" si="1"/>
         <v>100.07743534148985</v>
       </c>
-      <c r="R6">
+      <c r="W6">
         <f t="shared" si="2"/>
         <v>97.880589152603278</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -7412,49 +8658,64 @@
         <v>1.0859999999999901</v>
       </c>
       <c r="F7">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="G7">
         <v>0.97299999999999998</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.62385896324709</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>4.7295300029559499E-2</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.95895196510000003</v>
       </c>
-      <c r="K7">
+      <c r="L7">
+        <v>114.5</v>
+      </c>
+      <c r="M7">
         <v>67660</v>
       </c>
-      <c r="L7">
+      <c r="N7">
+        <v>7747070</v>
+      </c>
+      <c r="O7">
         <v>64460</v>
       </c>
-      <c r="M7">
+      <c r="P7">
+        <v>7380670</v>
+      </c>
+      <c r="Q7">
         <v>0.12882633400245999</v>
       </c>
-      <c r="N7">
+      <c r="R7">
+        <v>14.750615243281599</v>
+      </c>
+      <c r="S7">
         <v>64460</v>
       </c>
-      <c r="O7">
+      <c r="T7">
         <v>3200</v>
       </c>
-      <c r="P7">
+      <c r="U7">
         <f t="shared" si="0"/>
         <v>105.26756730294369</v>
       </c>
-      <c r="Q7">
+      <c r="V7">
         <f t="shared" si="1"/>
         <v>99.829642248722323</v>
       </c>
-      <c r="R7">
+      <c r="W7">
         <f t="shared" si="2"/>
         <v>94.834187591158198</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2001</v>
       </c>
@@ -7471,49 +8732,64 @@
         <v>1.075</v>
       </c>
       <c r="F8">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="G8">
         <v>0.96699999999999997</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.61926205827593395</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>5.0355450236966803E-2</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.95410414829999901</v>
       </c>
-      <c r="K8">
+      <c r="L8">
+        <v>113.3</v>
+      </c>
+      <c r="M8">
         <v>67520</v>
       </c>
-      <c r="L8">
+      <c r="N8">
+        <v>7650016</v>
+      </c>
+      <c r="O8">
         <v>64120</v>
       </c>
-      <c r="M8">
+      <c r="P8">
+        <v>7264796</v>
+      </c>
+      <c r="Q8">
         <v>0.127778428656596</v>
       </c>
-      <c r="N8">
+      <c r="R8">
+        <v>14.477295966792299</v>
+      </c>
+      <c r="S8">
         <v>64120</v>
       </c>
-      <c r="O8">
+      <c r="T8">
         <v>3400</v>
       </c>
-      <c r="P8">
+      <c r="U8">
         <f t="shared" si="0"/>
         <v>105.57106538604948</v>
       </c>
-      <c r="Q8">
+      <c r="V8">
         <f t="shared" si="1"/>
         <v>99.30308192659129</v>
       </c>
-      <c r="R8">
+      <c r="W8">
         <f t="shared" si="2"/>
         <v>94.062782793242079</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2002</v>
       </c>
@@ -7530,49 +8806,64 @@
         <v>1.06</v>
       </c>
       <c r="F9">
+        <v>1.022</v>
+      </c>
+      <c r="G9">
         <v>0.95799999999999996</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.61151539530461496</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>5.3670204813873502E-2</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.93493761139999998</v>
       </c>
-      <c r="K9">
+      <c r="L9">
+        <v>112.2</v>
+      </c>
+      <c r="M9">
         <v>66890</v>
       </c>
-      <c r="L9">
+      <c r="N9">
+        <v>7505058</v>
+      </c>
+      <c r="O9">
         <v>63300</v>
       </c>
-      <c r="M9">
+      <c r="P9">
+        <v>7102260</v>
+      </c>
+      <c r="Q9">
         <v>0.12603147913149501</v>
       </c>
-      <c r="N9">
+      <c r="R9">
+        <v>14.140731958553699</v>
+      </c>
+      <c r="S9">
         <v>63300</v>
       </c>
-      <c r="O9">
+      <c r="T9">
         <v>3590</v>
       </c>
-      <c r="P9">
+      <c r="U9">
         <f t="shared" si="0"/>
         <v>105.66559686234504</v>
       </c>
-      <c r="Q9">
+      <c r="V9">
         <f t="shared" si="1"/>
         <v>98.033142326157659</v>
       </c>
-      <c r="R9">
+      <c r="W9">
         <f t="shared" si="2"/>
         <v>92.776783775583553</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2003</v>
       </c>
@@ -7589,49 +8880,64 @@
         <v>1.0409999999999999</v>
       </c>
       <c r="F10">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="G10">
         <v>0.95499999999999996</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.60716465219648597</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>5.2505250525052498E-2</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.92780748660000001</v>
       </c>
-      <c r="K10">
+      <c r="L10">
+        <v>112.2</v>
+      </c>
+      <c r="M10">
         <v>66660</v>
       </c>
-      <c r="L10">
+      <c r="N10">
+        <v>7479252</v>
+      </c>
+      <c r="O10">
         <v>63160</v>
       </c>
-      <c r="M10">
+      <c r="P10">
+        <v>7086552</v>
+      </c>
+      <c r="Q10">
         <v>0.124006217892547</v>
       </c>
-      <c r="N10">
+      <c r="R10">
+        <v>13.913497647543799</v>
+      </c>
+      <c r="S10">
         <v>63160</v>
       </c>
-      <c r="O10">
+      <c r="T10">
         <v>3500</v>
       </c>
-      <c r="P10">
+      <c r="U10">
         <f t="shared" si="0"/>
         <v>107.15380395969791</v>
       </c>
-      <c r="Q10">
+      <c r="V10">
         <f t="shared" si="1"/>
         <v>97.816323369986051</v>
       </c>
-      <c r="R10">
+      <c r="W10">
         <f t="shared" si="2"/>
         <v>91.28590843753544</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2004</v>
       </c>
@@ -7648,49 +8954,64 @@
         <v>1.028</v>
       </c>
       <c r="F11">
+        <v>1.006</v>
+      </c>
+      <c r="G11">
         <v>0.95499999999999996</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.60352739134780498</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>4.7124360132490203E-2</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.92170818509999997</v>
       </c>
-      <c r="K11">
+      <c r="L11">
+        <v>112.4</v>
+      </c>
+      <c r="M11">
         <v>66420</v>
       </c>
-      <c r="L11">
+      <c r="N11">
+        <v>7465608</v>
+      </c>
+      <c r="O11">
         <v>63290</v>
       </c>
-      <c r="M11">
+      <c r="P11">
+        <v>7113796</v>
+      </c>
+      <c r="Q11">
         <v>0.121694669307475</v>
       </c>
-      <c r="N11">
+      <c r="R11">
+        <v>13.678480830160201</v>
+      </c>
+      <c r="S11">
         <v>63290</v>
       </c>
-      <c r="O11">
+      <c r="T11">
         <v>3130</v>
       </c>
-      <c r="P11">
+      <c r="U11">
         <f t="shared" si="0"/>
         <v>109.4138939686414</v>
       </c>
-      <c r="Q11">
+      <c r="V11">
         <f t="shared" si="1"/>
         <v>98.017655257859687</v>
       </c>
-      <c r="R11">
+      <c r="W11">
         <f t="shared" si="2"/>
         <v>89.584285599004517</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -7707,49 +9028,64 @@
         <v>1.0149999999999999</v>
       </c>
       <c r="F12">
+        <v>0.997</v>
+      </c>
+      <c r="G12">
         <v>0.95199999999999996</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.603281721951617</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>4.4354232446248601E-2</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.93375111909999997</v>
       </c>
-      <c r="K12">
+      <c r="L12">
+        <v>111.7</v>
+      </c>
+      <c r="M12">
         <v>66510</v>
       </c>
-      <c r="L12">
+      <c r="N12">
+        <v>7429167</v>
+      </c>
+      <c r="O12">
         <v>63560</v>
       </c>
-      <c r="M12">
+      <c r="P12">
+        <v>7099652</v>
+      </c>
+      <c r="Q12">
         <v>0.120050570800982</v>
       </c>
-      <c r="N12">
+      <c r="R12">
+        <v>13.4096487584697</v>
+      </c>
+      <c r="S12">
         <v>63560</v>
       </c>
-      <c r="O12">
+      <c r="T12">
         <v>2950</v>
       </c>
-      <c r="P12">
+      <c r="U12">
         <f t="shared" si="0"/>
         <v>111.38548314503277</v>
       </c>
-      <c r="Q12">
+      <c r="V12">
         <f t="shared" si="1"/>
         <v>98.435806101904916</v>
       </c>
-      <c r="R12">
+      <c r="W12">
         <f t="shared" si="2"/>
         <v>88.373999306295289</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2006</v>
       </c>
@@ -7766,49 +9102,64 @@
         <v>1.0049999999999999</v>
       </c>
       <c r="F13">
+        <v>0.997</v>
+      </c>
+      <c r="G13">
         <v>0.95499999999999996</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.60326254232071397</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>4.1266506602641001E-2</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.93137254899999999</v>
       </c>
-      <c r="K13">
+      <c r="L13">
+        <v>112.2</v>
+      </c>
+      <c r="M13">
         <v>66640</v>
       </c>
-      <c r="L13">
+      <c r="N13">
+        <v>7477008</v>
+      </c>
+      <c r="O13">
         <v>63890</v>
       </c>
-      <c r="M13">
+      <c r="P13">
+        <v>7168458</v>
+      </c>
+      <c r="Q13">
         <v>0.118781887873081</v>
       </c>
-      <c r="N13">
+      <c r="R13">
+        <v>13.3273278193597</v>
+      </c>
+      <c r="S13">
         <v>63890</v>
       </c>
-      <c r="O13">
+      <c r="T13">
         <v>2750</v>
       </c>
-      <c r="P13">
+      <c r="U13">
         <f t="shared" si="0"/>
         <v>113.15965075006372</v>
       </c>
-      <c r="Q13">
+      <c r="V13">
         <f t="shared" si="1"/>
         <v>98.946879355737963</v>
       </c>
-      <c r="R13">
+      <c r="W13">
         <f t="shared" si="2"/>
         <v>87.440071350416616</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2007</v>
       </c>
@@ -7825,49 +9176,64 @@
         <v>0.995</v>
       </c>
       <c r="F14">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="G14">
         <v>0.95499999999999996</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.60357594365179701</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>3.84500299222022E-2</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.92908438059999998</v>
       </c>
-      <c r="K14">
+      <c r="L14">
+        <v>111.4</v>
+      </c>
+      <c r="M14">
         <v>66840</v>
       </c>
-      <c r="L14">
+      <c r="N14">
+        <v>7445976</v>
+      </c>
+      <c r="O14">
         <v>64270</v>
       </c>
-      <c r="M14">
+      <c r="P14">
+        <v>7159678</v>
+      </c>
+      <c r="Q14">
         <v>0.11742938617198</v>
       </c>
-      <c r="N14">
+      <c r="R14">
+        <v>13.081633619558501</v>
+      </c>
+      <c r="S14">
         <v>64270</v>
       </c>
-      <c r="O14">
+      <c r="T14">
         <v>2570</v>
       </c>
-      <c r="P14">
+      <c r="U14">
         <f t="shared" si="0"/>
         <v>115.14376948695136</v>
       </c>
-      <c r="Q14">
+      <c r="V14">
         <f t="shared" si="1"/>
         <v>99.535387951060855</v>
       </c>
-      <c r="R14">
+      <c r="W14">
         <f t="shared" si="2"/>
         <v>86.444441062302275</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2008</v>
       </c>
@@ -7884,49 +9250,64 @@
         <v>0.98599999999999999</v>
       </c>
       <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
         <v>0.96799999999999997</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.60176001731164497</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>3.9706323044650799E-2</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.93738656989999902</v>
       </c>
-      <c r="K15">
+      <c r="L15">
+        <v>110.2</v>
+      </c>
+      <c r="M15">
         <v>66740</v>
       </c>
-      <c r="L15">
+      <c r="N15">
+        <v>7354748</v>
+      </c>
+      <c r="O15">
         <v>64090</v>
       </c>
-      <c r="M15">
+      <c r="P15">
+        <v>7062718</v>
+      </c>
+      <c r="Q15">
         <v>0.118481485328544</v>
       </c>
-      <c r="N15">
+      <c r="R15">
+        <v>13.0566596832056</v>
+      </c>
+      <c r="S15">
         <v>64090</v>
       </c>
-      <c r="O15">
+      <c r="T15">
         <v>2650</v>
       </c>
-      <c r="P15">
+      <c r="U15">
         <f t="shared" si="0"/>
         <v>113.80169099073602</v>
       </c>
-      <c r="Q15">
+      <c r="V15">
         <f t="shared" si="1"/>
         <v>99.256620721697388</v>
       </c>
-      <c r="R15">
+      <c r="W15">
         <f t="shared" si="2"/>
         <v>87.218933091053401</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2009</v>
       </c>
@@ -7943,49 +9324,64 @@
         <v>0.98199999999999998</v>
       </c>
       <c r="F16">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="G16">
         <v>0.95499999999999996</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.59898577746552395</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>5.05263157894736E-2</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.92803738319999995</v>
       </c>
-      <c r="K16">
+      <c r="L16">
+        <v>107</v>
+      </c>
+      <c r="M16">
         <v>66500</v>
       </c>
-      <c r="L16">
+      <c r="N16">
+        <v>7115500</v>
+      </c>
+      <c r="O16">
         <v>63140</v>
       </c>
-      <c r="M16">
+      <c r="P16">
+        <v>6755980</v>
+      </c>
+      <c r="Q16">
         <v>0.12416546963854</v>
       </c>
-      <c r="N16">
+      <c r="R16">
+        <v>13.285705251323799</v>
+      </c>
+      <c r="S16">
         <v>63140</v>
       </c>
-      <c r="O16">
+      <c r="T16">
         <v>3360</v>
       </c>
-      <c r="P16">
+      <c r="U16">
         <f t="shared" si="0"/>
         <v>106.98248359288895</v>
       </c>
-      <c r="Q16">
+      <c r="V16">
         <f t="shared" si="1"/>
         <v>97.785349233390122</v>
       </c>
-      <c r="R16">
+      <c r="W16">
         <f t="shared" si="2"/>
         <v>91.403139980842468</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2010</v>
       </c>
@@ -8002,49 +9398,64 @@
         <v>0.96299999999999997</v>
       </c>
       <c r="F17">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="G17">
         <v>0.94799999999999995</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.59611339816995301</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>5.0361881785283398E-2</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.91988950279999904</v>
       </c>
-      <c r="K17">
+      <c r="L17">
+        <v>108.6</v>
+      </c>
+      <c r="M17">
         <v>66320</v>
       </c>
-      <c r="L17">
+      <c r="N17">
+        <v>7202352</v>
+      </c>
+      <c r="O17">
         <v>62980</v>
       </c>
-      <c r="M17">
+      <c r="P17">
+        <v>6839628</v>
+      </c>
+      <c r="Q17">
         <v>0.11888851600620599</v>
       </c>
-      <c r="N17">
+      <c r="R17">
+        <v>12.911292838274001</v>
+      </c>
+      <c r="S17">
         <v>62980</v>
       </c>
-      <c r="O17">
+      <c r="T17">
         <v>3340</v>
       </c>
-      <c r="P17">
+      <c r="U17">
         <f t="shared" si="0"/>
         <v>111.4478472441502</v>
       </c>
-      <c r="Q17">
+      <c r="V17">
         <f t="shared" si="1"/>
         <v>97.537556140622584</v>
       </c>
-      <c r="R17">
+      <c r="W17">
         <f t="shared" si="2"/>
         <v>87.518564559570038</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2011</v>
       </c>
@@ -8061,49 +9472,64 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="F18">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="G18">
         <v>0.94499999999999995</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.59354443934526502</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>4.5936931473620303E-2</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.9205909511</v>
       </c>
-      <c r="K18">
+      <c r="L18">
+        <v>108.3</v>
+      </c>
+      <c r="M18">
         <v>65960</v>
       </c>
-      <c r="L18">
+      <c r="N18">
+        <v>7143468</v>
+      </c>
+      <c r="O18">
         <v>62930</v>
       </c>
-      <c r="M18">
+      <c r="P18">
+        <v>6815319</v>
+      </c>
+      <c r="Q18">
         <v>0.119043384908868</v>
       </c>
-      <c r="N18">
+      <c r="R18">
+        <v>12.892398585630399</v>
+      </c>
+      <c r="S18">
         <v>62930</v>
       </c>
-      <c r="O18">
+      <c r="T18">
         <v>3030</v>
       </c>
-      <c r="P18">
+      <c r="U18">
         <f t="shared" si="0"/>
         <v>111.21449606373157</v>
       </c>
-      <c r="Q18">
+      <c r="V18">
         <f t="shared" si="1"/>
         <v>97.460120799132724</v>
       </c>
-      <c r="R18">
+      <c r="W18">
         <f t="shared" si="2"/>
         <v>87.63256971760508</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2012</v>
       </c>
@@ -8120,49 +9546,64 @@
         <v>0.94099999999999995</v>
       </c>
       <c r="F19">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="G19">
         <v>0.94499999999999995</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.59119644111449299</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>4.3412033511043398E-2</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.90725436179999996</v>
       </c>
-      <c r="K19">
+      <c r="L19">
+        <v>108.9</v>
+      </c>
+      <c r="M19">
         <v>65650</v>
       </c>
-      <c r="L19">
+      <c r="N19">
+        <v>7149285</v>
+      </c>
+      <c r="O19">
         <v>62800</v>
       </c>
-      <c r="M19">
+      <c r="P19">
+        <v>6838920</v>
+      </c>
+      <c r="Q19">
         <v>0.116932088929237</v>
       </c>
-      <c r="N19">
+      <c r="R19">
+        <v>12.7339044843939</v>
+      </c>
+      <c r="S19">
         <v>62800</v>
       </c>
-      <c r="O19">
+      <c r="T19">
         <v>2850</v>
       </c>
-      <c r="P19">
+      <c r="U19">
         <f t="shared" si="0"/>
         <v>112.98866291562295</v>
       </c>
-      <c r="Q19">
+      <c r="V19">
         <f t="shared" si="1"/>
         <v>97.258788911259103</v>
       </c>
-      <c r="R19">
+      <c r="W19">
         <f t="shared" si="2"/>
         <v>86.07836078553251</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2013</v>
       </c>
@@ -8179,49 +9620,64 @@
         <v>0.93899999999999995</v>
       </c>
       <c r="F20">
+        <v>0.95</v>
+      </c>
+      <c r="G20">
         <v>0.94899999999999995</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.59383556708459395</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>4.0497497345669597E-2</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.91457753019999999</v>
       </c>
-      <c r="K20">
+      <c r="L20">
+        <v>107.7</v>
+      </c>
+      <c r="M20">
         <v>65930</v>
       </c>
-      <c r="L20">
+      <c r="N20">
+        <v>7100661</v>
+      </c>
+      <c r="O20">
         <v>63260</v>
       </c>
-      <c r="M20">
+      <c r="P20">
+        <v>6813102</v>
+      </c>
+      <c r="Q20">
         <v>0.115442151473909</v>
       </c>
-      <c r="N20">
+      <c r="R20">
+        <v>12.43311971374</v>
+      </c>
+      <c r="S20">
         <v>63260</v>
       </c>
-      <c r="O20">
+      <c r="T20">
         <v>2670</v>
       </c>
-      <c r="P20">
+      <c r="U20">
         <f t="shared" si="0"/>
         <v>115.28524034841119</v>
       </c>
-      <c r="Q20">
+      <c r="V20">
         <f t="shared" si="1"/>
         <v>97.971194052965771</v>
       </c>
-      <c r="R20">
+      <c r="W20">
         <f t="shared" si="2"/>
         <v>84.981558573222827</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2014</v>
       </c>
@@ -8238,49 +9694,64 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="F21">
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="G21">
         <v>0.97499999999999998</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.595383950127923</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>3.6011499470419102E-2</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.92264678469999994</v>
       </c>
-      <c r="K21">
+      <c r="L21">
+        <v>107.3</v>
+      </c>
+      <c r="M21">
         <v>66090</v>
       </c>
-      <c r="L21">
+      <c r="N21">
+        <v>7091457</v>
+      </c>
+      <c r="O21">
         <v>63710</v>
       </c>
-      <c r="M21">
+      <c r="P21">
+        <v>6836083</v>
+      </c>
+      <c r="Q21">
         <v>0.115186014952985</v>
       </c>
-      <c r="N21">
+      <c r="R21">
+        <v>12.359459404455301</v>
+      </c>
+      <c r="S21">
         <v>63710</v>
       </c>
-      <c r="O21">
+      <c r="T21">
         <v>2380</v>
       </c>
-      <c r="P21">
+      <c r="U21">
         <f t="shared" si="0"/>
         <v>116.36350265024547</v>
       </c>
-      <c r="Q21">
+      <c r="V21">
         <f t="shared" si="1"/>
         <v>98.668112126374467</v>
       </c>
-      <c r="R21">
+      <c r="W21">
         <f t="shared" si="2"/>
         <v>84.793006294200211</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2015</v>
       </c>
@@ -8297,49 +9768,64 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="F22">
+        <v>0.97399999999999998</v>
+      </c>
+      <c r="G22">
         <v>0.98199999999999998</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.59573052298395801</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>3.3660377358490499E-2</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.92703461180000002</v>
       </c>
-      <c r="K22">
+      <c r="L22">
+        <v>106.9</v>
+      </c>
+      <c r="M22">
         <v>66250</v>
       </c>
-      <c r="L22">
+      <c r="N22">
+        <v>7082125</v>
+      </c>
+      <c r="O22">
         <v>64020</v>
       </c>
-      <c r="M22">
+      <c r="P22">
+        <v>6843738</v>
+      </c>
+      <c r="Q22">
         <v>0.113724334159824</v>
       </c>
-      <c r="N22">
+      <c r="R22">
+        <v>12.157131321685201</v>
+      </c>
+      <c r="S22">
         <v>64020</v>
       </c>
-      <c r="O22">
+      <c r="T22">
         <v>2230</v>
       </c>
-      <c r="P22">
+      <c r="U22">
         <f t="shared" si="0"/>
         <v>118.43258286778007</v>
       </c>
-      <c r="Q22">
+      <c r="V22">
         <f t="shared" si="1"/>
         <v>99.148211243611584</v>
       </c>
-      <c r="R22">
+      <c r="W22">
         <f t="shared" si="2"/>
         <v>83.717004934615119</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2016</v>
       </c>
@@ -8356,55 +9842,70 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="F23">
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="G23">
         <v>0.98099999999999998</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.60036140354031597</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>3.11470500149745E-2</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.937911571</v>
       </c>
-      <c r="K23">
+      <c r="L23">
+        <v>106.3</v>
+      </c>
+      <c r="M23">
         <v>66780</v>
       </c>
-      <c r="L23">
+      <c r="N23">
+        <v>7098714</v>
+      </c>
+      <c r="O23">
         <v>64700</v>
       </c>
-      <c r="M23">
+      <c r="P23">
+        <v>6877610</v>
+      </c>
+      <c r="Q23">
         <v>0.114161971874052</v>
       </c>
-      <c r="N23">
+      <c r="R23">
+        <v>12.1354176102117</v>
+      </c>
+      <c r="S23">
         <v>64700</v>
       </c>
-      <c r="O23">
+      <c r="T23">
         <v>2080</v>
       </c>
-      <c r="P23">
+      <c r="U23">
         <f t="shared" si="0"/>
         <v>119.23170459257688</v>
       </c>
-      <c r="Q23">
+      <c r="V23">
         <f t="shared" si="1"/>
         <v>100.20133188787364</v>
       </c>
-      <c r="R23">
+      <c r="W23">
         <f t="shared" si="2"/>
         <v>84.039167459920691</v>
       </c>
-      <c r="T23" t="s">
+      <c r="Y23" t="s">
         <v>18</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AG23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2017</v>
       </c>
@@ -8421,49 +9922,64 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="F24">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="G24">
         <v>0.98599999999999999</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>0.60497133305774697</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>0</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>2.82234105763517E-2</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>0.94439208289999999</v>
       </c>
-      <c r="K24">
+      <c r="L24">
+        <v>106.1</v>
+      </c>
+      <c r="M24">
         <v>67320</v>
       </c>
-      <c r="L24">
+      <c r="N24">
+        <v>7142652</v>
+      </c>
+      <c r="O24">
         <v>65420</v>
       </c>
-      <c r="M24">
+      <c r="P24">
+        <v>6941062</v>
+      </c>
+      <c r="Q24">
         <v>0.113563727285757</v>
       </c>
-      <c r="N24">
+      <c r="R24">
+        <v>12.0491114650188</v>
+      </c>
+      <c r="S24">
         <v>65420</v>
       </c>
-      <c r="O24">
+      <c r="T24">
         <v>1900</v>
       </c>
-      <c r="P24">
+      <c r="U24">
         <f t="shared" si="0"/>
         <v>121.19364165596625</v>
       </c>
-      <c r="Q24">
+      <c r="V24">
         <f t="shared" si="1"/>
         <v>101.31640080532756</v>
       </c>
-      <c r="R24">
+      <c r="W24">
         <f t="shared" si="2"/>
         <v>83.598775827642484</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2018</v>
       </c>
@@ -8480,49 +9996,64 @@
         <v>0.98</v>
       </c>
       <c r="F25">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="G25">
         <v>0.995</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.615496603041087</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>0</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>2.43831216235946E-2</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>0.9657794677</v>
       </c>
-      <c r="K25">
+      <c r="L25">
+        <v>105.2</v>
+      </c>
+      <c r="M25">
         <v>68490</v>
       </c>
-      <c r="L25">
+      <c r="N25">
+        <v>7205148</v>
+      </c>
+      <c r="O25">
         <v>66820</v>
       </c>
-      <c r="M25">
+      <c r="P25">
+        <v>7029464</v>
+      </c>
+      <c r="Q25">
         <v>0.11505437461071499</v>
       </c>
-      <c r="N25">
+      <c r="R25">
+        <v>12.1037202090472</v>
+      </c>
+      <c r="S25">
         <v>66820</v>
       </c>
-      <c r="O25">
+      <c r="T25">
         <v>1670</v>
       </c>
-      <c r="P25">
+      <c r="U25">
         <f t="shared" si="0"/>
         <v>122.18341768984907</v>
       </c>
-      <c r="Q25">
+      <c r="V25">
         <f t="shared" si="1"/>
         <v>103.48459036704352</v>
       </c>
-      <c r="R25">
+      <c r="W25">
         <f t="shared" si="2"/>
         <v>84.69610060321709</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2019</v>
       </c>
@@ -8539,49 +10070,64 @@
         <v>0.98699999999999999</v>
       </c>
       <c r="F26">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.62104657849338696</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>2.34375E-2</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>0.98347910589999998</v>
       </c>
-      <c r="K26">
+      <c r="L26">
+        <v>102.9</v>
+      </c>
+      <c r="M26">
         <v>69120</v>
       </c>
-      <c r="L26">
+      <c r="N26">
+        <v>7112448</v>
+      </c>
+      <c r="O26">
         <v>67500</v>
       </c>
-      <c r="M26">
+      <c r="P26">
+        <v>6945750</v>
+      </c>
+      <c r="Q26">
         <v>0.116505898523707</v>
       </c>
-      <c r="N26">
+      <c r="R26">
+        <v>11.9884569580895</v>
+      </c>
+      <c r="S26">
         <v>67500</v>
       </c>
-      <c r="O26">
+      <c r="T26">
         <v>1620</v>
       </c>
-      <c r="P26">
+      <c r="U26">
         <f t="shared" si="0"/>
         <v>121.88907829368263</v>
       </c>
-      <c r="Q26">
+      <c r="V26">
         <f t="shared" si="1"/>
         <v>104.53771101130556</v>
       </c>
-      <c r="R26">
+      <c r="W26">
         <f t="shared" si="2"/>
         <v>85.76462507939371</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -8601,46 +10147,61 @@
         <v>1</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
         <v>0.62116384973990602</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>0</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>2.7818023761228598E-2</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>1</v>
       </c>
-      <c r="K27">
+      <c r="L27">
+        <v>100</v>
+      </c>
+      <c r="M27">
         <v>69020</v>
       </c>
-      <c r="L27">
+      <c r="N27">
+        <v>6902000</v>
+      </c>
+      <c r="O27">
         <v>67100</v>
       </c>
-      <c r="M27">
+      <c r="P27">
+        <v>6710000</v>
+      </c>
+      <c r="Q27">
         <v>0.121102869939488</v>
       </c>
-      <c r="N27">
+      <c r="R27">
+        <v>12.110286993948799</v>
+      </c>
+      <c r="S27">
         <v>67100</v>
       </c>
-      <c r="O27">
+      <c r="T27">
         <v>1920</v>
       </c>
-      <c r="P27">
+      <c r="U27">
         <f t="shared" si="0"/>
         <v>116.56737553142256</v>
       </c>
-      <c r="Q27">
+      <c r="V27">
         <f t="shared" si="1"/>
         <v>103.91822827938671</v>
       </c>
-      <c r="R27">
+      <c r="W27">
         <f t="shared" si="2"/>
         <v>89.148638549706334</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -8657,49 +10218,64 @@
         <v>0.999</v>
       </c>
       <c r="F28">
+        <v>1.01</v>
+      </c>
+      <c r="G28">
         <v>0.998</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>0.62374136451889595</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>0</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>2.8087447517011699E-2</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>0.99602780540000002</v>
       </c>
-      <c r="K28">
+      <c r="L28">
+        <v>100.7</v>
+      </c>
+      <c r="M28">
         <v>69070</v>
       </c>
-      <c r="L28">
+      <c r="N28">
+        <v>6955349</v>
+      </c>
+      <c r="O28">
         <v>67130</v>
       </c>
-      <c r="M28">
+      <c r="P28">
+        <v>6759991</v>
+      </c>
+      <c r="Q28">
         <v>0.116922102457455</v>
       </c>
-      <c r="N28">
+      <c r="R28">
+        <v>11.774055717465799</v>
+      </c>
+      <c r="S28">
         <v>67130</v>
       </c>
-      <c r="O28">
+      <c r="T28">
         <v>1940</v>
       </c>
-      <c r="P28">
+      <c r="U28">
         <f t="shared" si="0"/>
         <v>120.78943917774608</v>
       </c>
-      <c r="Q28">
+      <c r="V28">
         <f t="shared" si="1"/>
         <v>103.96468948428061</v>
       </c>
-      <c r="R28">
+      <c r="W28">
         <f t="shared" si="2"/>
         <v>86.071009346514785</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2022</v>
       </c>
@@ -8716,49 +10292,64 @@
         <v>1.006</v>
       </c>
       <c r="F29">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="G29">
         <v>1.0229999999999999</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.62482460190289901</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>0</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>2.5934511735728701E-2</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>1.0148809519999999</v>
       </c>
-      <c r="K29">
+      <c r="L29">
+        <v>100.8</v>
+      </c>
+      <c r="M29">
         <v>69020</v>
       </c>
-      <c r="L29">
+      <c r="N29">
+        <v>6957216</v>
+      </c>
+      <c r="O29">
         <v>67230</v>
       </c>
-      <c r="M29">
+      <c r="P29">
+        <v>6776784</v>
+      </c>
+      <c r="Q29">
         <v>0.11563226298622301</v>
       </c>
-      <c r="N29">
+      <c r="R29">
+        <v>11.6557321090113</v>
+      </c>
+      <c r="S29">
         <v>67230</v>
       </c>
-      <c r="O29">
+      <c r="T29">
         <v>1790</v>
       </c>
-      <c r="P29">
+      <c r="U29">
         <f t="shared" si="0"/>
         <v>122.31874595561472</v>
       </c>
-      <c r="Q29">
+      <c r="V29">
         <f t="shared" si="1"/>
         <v>104.11956016726035</v>
       </c>
-      <c r="R29">
+      <c r="W29">
         <f t="shared" si="2"/>
         <v>85.12150721774222</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2023</v>
       </c>
@@ -8775,49 +10366,64 @@
         <v>1.0509999999999999</v>
       </c>
       <c r="F30">
+        <v>1.079</v>
+      </c>
+      <c r="G30">
         <v>1.056</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.62836869135981699</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>2.5703971119133501E-2</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1.0257680870000001</v>
       </c>
-      <c r="K30">
+      <c r="L30">
+        <v>100.9</v>
+      </c>
+      <c r="M30">
         <v>69250</v>
       </c>
-      <c r="L30">
+      <c r="N30">
+        <v>6987325</v>
+      </c>
+      <c r="O30">
         <v>67470</v>
       </c>
-      <c r="M30">
+      <c r="P30">
+        <v>6807723</v>
+      </c>
+      <c r="Q30">
         <v>0.115109044483006</v>
       </c>
-      <c r="N30">
+      <c r="R30">
+        <v>11.6145025883353</v>
+      </c>
+      <c r="S30">
         <v>67470</v>
       </c>
-      <c r="O30">
+      <c r="T30">
         <v>1780</v>
       </c>
-      <c r="P30">
+      <c r="U30">
         <f t="shared" si="0"/>
         <v>123.31337807063348</v>
       </c>
-      <c r="Q30">
+      <c r="V30">
         <f t="shared" si="1"/>
         <v>104.49124980641164</v>
       </c>
-      <c r="R30">
+      <c r="W30">
         <f t="shared" si="2"/>
         <v>84.73634527030751</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2024</v>
       </c>
@@ -8834,49 +10440,64 @@
         <v>1.085</v>
       </c>
       <c r="F31">
+        <v>1.1059999999999901</v>
+      </c>
+      <c r="G31">
         <v>1.085</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.63286302977376296</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>2.5298260744573801E-2</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>1.065141004</v>
       </c>
-      <c r="K31">
+      <c r="L31">
+        <v>99.891000000000005</v>
+      </c>
+      <c r="M31">
         <v>69570</v>
       </c>
-      <c r="L31">
+      <c r="N31">
+        <v>6949416.8700000001</v>
+      </c>
+      <c r="O31">
         <v>67810</v>
       </c>
-      <c r="M31">
+      <c r="P31">
+        <v>6773608.71</v>
+      </c>
+      <c r="Q31">
         <v>0.11600572981870801</v>
       </c>
-      <c r="N31">
+      <c r="R31">
+        <v>11.5879283573205</v>
+      </c>
+      <c r="S31">
         <v>67810</v>
       </c>
-      <c r="O31">
+      <c r="T31">
         <v>1760</v>
       </c>
-      <c r="P31">
+      <c r="U31">
         <f t="shared" si="0"/>
         <v>122.97681401031085</v>
       </c>
-      <c r="Q31">
+      <c r="V31">
         <f t="shared" si="1"/>
         <v>105.01781012854268</v>
       </c>
-      <c r="R31">
+      <c r="W31">
         <f t="shared" si="2"/>
         <v>85.396431005065381</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2025</v>
       </c>
@@ -8893,49 +10514,64 @@
         <v>1.1220000000000001</v>
       </c>
       <c r="F32">
+        <v>1.139</v>
+      </c>
+      <c r="G32">
         <v>1.119</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.63888204763338097</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>0</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>2.51284980011422E-2</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>1.1051107979999999</v>
       </c>
-      <c r="K32">
+      <c r="L32">
+        <v>98.492525999999998</v>
+      </c>
+      <c r="M32">
         <v>70040</v>
       </c>
-      <c r="L32">
+      <c r="N32">
+        <v>6898416.52104</v>
+      </c>
+      <c r="O32">
         <v>68280</v>
       </c>
-      <c r="M32">
+      <c r="P32">
+        <v>6725069.6752800001</v>
+      </c>
+      <c r="Q32">
         <v>0.11541893399891701</v>
       </c>
-      <c r="N32">
+      <c r="R32">
+        <v>11.3679023577807</v>
+      </c>
+      <c r="S32">
         <v>68280</v>
       </c>
-      <c r="O32">
+      <c r="T32">
         <v>1760</v>
       </c>
-      <c r="P32">
+      <c r="U32">
         <f t="shared" si="0"/>
         <v>124.45873638773175</v>
       </c>
-      <c r="Q32">
+      <c r="V32">
         <f t="shared" si="1"/>
         <v>105.74570233854732</v>
       </c>
-      <c r="R32">
+      <c r="W32">
         <f t="shared" si="2"/>
         <v>84.964467266575085</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2026</v>
       </c>
@@ -8952,49 +10588,64 @@
         <v>1.1444399999999999</v>
       </c>
       <c r="F33">
+        <v>1.16178</v>
+      </c>
+      <c r="G33">
         <v>1.140261</v>
       </c>
-      <c r="G33">
-        <v>0.64467479231399905</v>
-      </c>
       <c r="H33">
+        <v>0.65504006149607996</v>
+      </c>
+      <c r="I33">
         <v>4.6452785208657102E-2</v>
       </c>
-      <c r="I33">
-        <v>2.2791292000568099E-2</v>
-      </c>
       <c r="J33">
-        <v>1.1312078489858199</v>
+        <v>7.8665162741282397E-3</v>
       </c>
       <c r="K33">
-        <v>70467.921958304098</v>
+        <v>1.1440817534510399</v>
       </c>
       <c r="L33">
-        <v>69073.594231087205</v>
+        <v>92.5419540954491</v>
       </c>
       <c r="M33">
-        <v>0.11517951208272</v>
+        <v>71599.808961890507</v>
       </c>
       <c r="N33">
-        <v>68861.866972279196</v>
+        <v>6625986.2341941902</v>
       </c>
       <c r="O33">
-        <v>1606.05498602495</v>
+        <v>73629.847564697906</v>
       </c>
       <c r="P33">
+        <v>6813849.9733871901</v>
+      </c>
+      <c r="Q33">
+        <v>0.122777017927498</v>
+      </c>
+      <c r="R33">
+        <v>11.3620251570227</v>
+      </c>
+      <c r="S33">
+        <v>71036.567899467307</v>
+      </c>
+      <c r="T33">
+        <v>563.24106242318396</v>
+      </c>
+      <c r="U33">
         <f t="shared" si="0"/>
         <v>126.1669935538377</v>
       </c>
-      <c r="Q33">
+      <c r="V33">
         <f t="shared" si="1"/>
-        <v>106.97474714431966</v>
-      </c>
-      <c r="R33">
+        <v>110.01481787125182</v>
+      </c>
+      <c r="W33">
         <f t="shared" si="2"/>
-        <v>84.78821927279391</v>
+        <v>87.197780316693169</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2027</v>
       </c>
@@ -9011,49 +10662,64 @@
         <v>1.1570288399999999</v>
       </c>
       <c r="F34">
+        <v>1.1745595799999999</v>
+      </c>
+      <c r="G34">
         <v>1.1562246539999901</v>
       </c>
-      <c r="G34">
-        <v>0.65231465634782804</v>
-      </c>
       <c r="H34">
+        <v>0.679709723857712</v>
+      </c>
+      <c r="I34">
         <v>4.1807506687791401E-2</v>
       </c>
-      <c r="I34">
-        <v>2.1126384134101499E-2</v>
-      </c>
       <c r="J34">
-        <v>1.15674908041497</v>
+        <v>5.0902625590218201E-3</v>
       </c>
       <c r="K34">
-        <v>71066.777852032101</v>
+        <v>1.1842283705605401</v>
       </c>
       <c r="L34">
-        <v>69839.201394407006</v>
+        <v>88.978807218882494</v>
       </c>
       <c r="M34">
-        <v>0.115883043199139</v>
+        <v>74050.296155954595</v>
       </c>
       <c r="N34">
-        <v>69565.393803957195</v>
+        <v>6588907.0261618504</v>
       </c>
       <c r="O34">
-        <v>1501.38404807489</v>
+        <v>76766.179229139394</v>
       </c>
       <c r="P34">
+        <v>6830563.0625597797</v>
+      </c>
+      <c r="Q34">
+        <v>0.127376864085328</v>
+      </c>
+      <c r="R34">
+        <v>11.3338414335942</v>
+      </c>
+      <c r="S34">
+        <v>73673.360705947503</v>
+      </c>
+      <c r="T34">
+        <v>376.935450007133</v>
+      </c>
+      <c r="U34">
         <f t="shared" si="0"/>
         <v>126.79096484272354</v>
       </c>
-      <c r="Q34">
+      <c r="V34">
         <f t="shared" si="1"/>
-        <v>108.16044818709463</v>
-      </c>
-      <c r="R34">
+        <v>114.09843689940762</v>
+      </c>
+      <c r="W34">
         <f t="shared" si="2"/>
-        <v>85.306116505431646</v>
+        <v>89.989406611851066</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2028</v>
       </c>
@@ -9070,49 +10736,64 @@
         <v>1.1651280420000001</v>
       </c>
       <c r="F35">
+        <v>1.1827814969999999</v>
+      </c>
+      <c r="G35">
         <v>1.168943125</v>
       </c>
-      <c r="G35">
-        <v>0.66112044900899203</v>
-      </c>
       <c r="H35">
+        <v>0.69918509815293095</v>
+      </c>
+      <c r="I35">
         <v>3.7162228166925701E-2</v>
       </c>
-      <c r="I35">
-        <v>2.1121205375515598E-2</v>
-      </c>
       <c r="J35">
-        <v>1.1812412259655001</v>
+        <v>5.7865793466481503E-3</v>
       </c>
       <c r="K35">
-        <v>71775.0099946962</v>
+        <v>1.2234654913804499</v>
       </c>
       <c r="L35">
-        <v>70483.671680189902</v>
+        <v>86.950272169451594</v>
       </c>
       <c r="M35">
-        <v>0.116374574126548</v>
+        <v>75906.3309958748</v>
       </c>
       <c r="N35">
-        <v>70259.0352677685</v>
+        <v>6600076.1394758001</v>
       </c>
       <c r="O35">
-        <v>1515.97472692766</v>
+        <v>77935.886644214101</v>
       </c>
       <c r="P35">
+        <v>6776546.5554819396</v>
+      </c>
+      <c r="Q35">
+        <v>0.12867881881279</v>
+      </c>
+      <c r="R35">
+        <v>11.188658318215699</v>
+      </c>
+      <c r="S35">
+        <v>75467.0929886542</v>
+      </c>
+      <c r="T35">
+        <v>439.23800722056802</v>
+      </c>
+      <c r="U35">
         <f t="shared" si="0"/>
         <v>127.42051282006256</v>
       </c>
-      <c r="Q35">
+      <c r="V35">
         <f t="shared" si="1"/>
-        <v>109.15854372028791</v>
-      </c>
-      <c r="R35">
+        <v>116.87640233646306</v>
+      </c>
+      <c r="W35">
         <f t="shared" si="2"/>
-        <v>85.667951968170641</v>
+        <v>91.724950519945395</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2029</v>
       </c>
@@ -9129,49 +10810,64 @@
         <v>1.173283938</v>
       </c>
       <c r="F36">
+        <v>1.1910609679999999</v>
+      </c>
+      <c r="G36">
         <v>1.1818014999999999</v>
       </c>
-      <c r="G36">
-        <v>0.66895153064074597</v>
-      </c>
       <c r="H36">
+        <v>0.71445816826568798</v>
+      </c>
+      <c r="I36">
         <v>3.251694964606E-2</v>
       </c>
-      <c r="I36">
-        <v>2.1520012415980599E-2</v>
-      </c>
       <c r="J36">
-        <v>1.2058705857532499</v>
+        <v>9.7151107628826398E-3</v>
       </c>
       <c r="K36">
-        <v>72345.791809096394</v>
+        <v>1.26025140924879</v>
       </c>
       <c r="L36">
-        <v>70983.1643471141</v>
+        <v>85.981280989656696</v>
       </c>
       <c r="M36">
-        <v>0.11662023143024799</v>
+        <v>77265.793065261096</v>
       </c>
       <c r="N36">
-        <v>70788.9094711207</v>
+        <v>6643411.8644328797</v>
       </c>
       <c r="O36">
-        <v>1556.8823379757</v>
+        <v>77624.521647657399</v>
       </c>
       <c r="P36">
+        <v>6674255.8074749196</v>
+      </c>
+      <c r="Q36">
+        <v>0.12753150359632001</v>
+      </c>
+      <c r="R36">
+        <v>10.9653220457486</v>
+      </c>
+      <c r="S36">
+        <v>76515.147327450104</v>
+      </c>
+      <c r="T36">
+        <v>750.64573781098102</v>
+      </c>
+      <c r="U36">
         <f t="shared" si="0"/>
         <v>128.0531866835407</v>
       </c>
-      <c r="Q36">
+      <c r="V36">
         <f t="shared" si="1"/>
-        <v>109.932111424987</v>
-      </c>
-      <c r="R36">
+        <v>118.49953124895478</v>
+      </c>
+      <c r="W36">
         <f t="shared" si="2"/>
-        <v>85.848790078659647</v>
+        <v>92.539306766183032</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2030</v>
       </c>
@@ -9188,49 +10884,64 @@
         <v>1.1814969259999999</v>
       </c>
       <c r="F37">
+        <v>1.1993983939999999</v>
+      </c>
+      <c r="G37">
         <v>1.1948013159999999</v>
       </c>
-      <c r="G37">
-        <v>0.67617640454346895</v>
-      </c>
       <c r="H37">
+        <v>0.723289583142251</v>
+      </c>
+      <c r="I37">
         <v>2.7871671125194199E-2</v>
       </c>
-      <c r="I37">
-        <v>2.2281853059728299E-2</v>
-      </c>
       <c r="J37">
-        <v>1.23042167089837</v>
+        <v>1.7484126022216901E-2</v>
       </c>
       <c r="K37">
-        <v>72836.189322544495</v>
+        <v>1.2905356238150401</v>
       </c>
       <c r="L37">
-        <v>71351.654539158699</v>
+        <v>85.561245735490601</v>
       </c>
       <c r="M37">
-        <v>0.11664645629786199</v>
+        <v>77912.030606500193</v>
       </c>
       <c r="N37">
-        <v>71213.264054629093</v>
+        <v>6666250.3964738296</v>
       </c>
       <c r="O37">
-        <v>1622.9252679154899</v>
+        <v>76589.128430508397</v>
       </c>
       <c r="P37">
+        <v>6553061.2383097801</v>
+      </c>
+      <c r="Q37">
+        <v>0.12520873524324</v>
+      </c>
+      <c r="R37">
+        <v>10.713015364376799</v>
+      </c>
+      <c r="S37">
+        <v>76549.806844729304</v>
+      </c>
+      <c r="T37">
+        <v>1362.2237617708699</v>
+      </c>
+      <c r="U37">
         <f t="shared" si="0"/>
         <v>128.6890018752074</v>
       </c>
-      <c r="Q37">
+      <c r="V37">
         <f t="shared" si="1"/>
-        <v>110.50279470211973</v>
-      </c>
-      <c r="R37">
+        <v>118.55320868008255</v>
+      </c>
+      <c r="W37">
         <f t="shared" si="2"/>
-        <v>85.868095246613819</v>
+        <v>92.123807747802914</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2031</v>
       </c>
@@ -9247,49 +10958,64 @@
         <v>1.1897674039999999</v>
       </c>
       <c r="F38">
+        <v>1.2077941830000001</v>
+      </c>
+      <c r="G38">
         <v>1.2079441310000001</v>
       </c>
-      <c r="G38">
-        <v>0.68261595410904397</v>
-      </c>
       <c r="H38">
+        <v>0.72494380863208097</v>
+      </c>
+      <c r="I38">
         <v>2.3226392604328499E-2</v>
       </c>
-      <c r="I38">
-        <v>2.32299938698564E-2</v>
-      </c>
       <c r="J38">
-        <v>1.25459443694746</v>
+        <v>2.63961117497701E-2</v>
       </c>
       <c r="K38">
-        <v>73212.7836881033</v>
+        <v>1.3126670863688199</v>
       </c>
       <c r="L38">
-        <v>71604.7962080625</v>
+        <v>85.3792650584912</v>
       </c>
       <c r="M38">
-        <v>0.116481933843694</v>
+        <v>77753.848194833903</v>
       </c>
       <c r="N38">
-        <v>71512.051171833606</v>
+        <v>6638566.4143444104</v>
       </c>
       <c r="O38">
-        <v>1700.73251626976</v>
+        <v>75412.8411145133</v>
       </c>
       <c r="P38">
+        <v>6438692.9503299203</v>
+      </c>
+      <c r="Q38">
+        <v>0.12267660875873999</v>
+      </c>
+      <c r="R38">
+        <v>10.4740386956893</v>
+      </c>
+      <c r="S38">
+        <v>75701.448928908401</v>
+      </c>
+      <c r="T38">
+        <v>2052.39926592549</v>
+      </c>
+      <c r="U38">
         <f t="shared" si="0"/>
         <v>129.32797413466147</v>
       </c>
-      <c r="Q38">
+      <c r="V38">
         <f t="shared" si="1"/>
-        <v>110.89483693365727</v>
-      </c>
-      <c r="R38">
+        <v>117.23935098173828</v>
+      </c>
+      <c r="W38">
         <f t="shared" si="2"/>
-        <v>85.746983725415134</v>
+        <v>90.652739104738444</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2032</v>
       </c>
@@ -9306,49 +11032,64 @@
         <v>1.1980957759999999</v>
       </c>
       <c r="F39">
+        <v>1.2162487419999899</v>
+      </c>
+      <c r="G39">
         <v>1.221231516</v>
       </c>
-      <c r="G39">
-        <v>0.68826160753108101</v>
-      </c>
       <c r="H39">
+        <v>0.72236327920195598</v>
+      </c>
+      <c r="I39">
         <v>1.8581114083462798E-2</v>
       </c>
-      <c r="I39">
-        <v>2.4147574304665499E-2</v>
-      </c>
       <c r="J39">
-        <v>1.2782309343712299</v>
+        <v>3.18175737866737E-2</v>
       </c>
       <c r="K39">
-        <v>73465.884722657502</v>
+        <v>1.3297128546113199</v>
       </c>
       <c r="L39">
-        <v>71760.274108128302</v>
+        <v>85.289684526502796</v>
       </c>
       <c r="M39">
-        <v>0.116158101772195</v>
+        <v>77105.056422016802</v>
       </c>
       <c r="N39">
-        <v>71691.861812459101</v>
+        <v>6576265.9376320103</v>
       </c>
       <c r="O39">
-        <v>1774.02291019836</v>
+        <v>74430.598241660904</v>
       </c>
       <c r="P39">
+        <v>6348162.2431501402</v>
+      </c>
+      <c r="Q39">
+        <v>0.120480545998094</v>
+      </c>
+      <c r="R39">
+        <v>10.2757477597583</v>
+      </c>
+      <c r="S39">
+        <v>74651.760599983594</v>
+      </c>
+      <c r="T39">
+        <v>2453.2958220331502</v>
+      </c>
+      <c r="U39">
         <f t="shared" si="0"/>
         <v>129.97011896045797</v>
       </c>
-      <c r="Q39">
+      <c r="V39">
         <f t="shared" si="1"/>
-        <v>111.13562661937169</v>
-      </c>
-      <c r="R39">
+        <v>115.6136914975741</v>
+      </c>
+      <c r="W39">
         <f t="shared" si="2"/>
-        <v>85.508598059515151</v>
+        <v>88.954055303087273</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2033</v>
       </c>
@@ -9365,49 +11106,64 @@
         <v>1.2064824459999901</v>
       </c>
       <c r="F40">
+        <v>1.224762484</v>
+      </c>
+      <c r="G40">
         <v>1.234665063</v>
       </c>
-      <c r="G40">
-        <v>0.69334534765563105</v>
-      </c>
       <c r="H40">
+        <v>0.71987519351663598</v>
+      </c>
+      <c r="I40">
         <v>1.39358355625971E-2</v>
       </c>
-      <c r="I40">
-        <v>2.4964550552993601E-2</v>
-      </c>
       <c r="J40">
-        <v>1.30149055090067</v>
+        <v>3.3771863076131899E-2</v>
       </c>
       <c r="K40">
-        <v>73628.867571187293</v>
+        <v>1.34498988625422</v>
       </c>
       <c r="L40">
-        <v>71835.867106205405</v>
+        <v>85.232011914010897</v>
       </c>
       <c r="M40">
-        <v>0.115705955628706</v>
+        <v>76444.986549918598</v>
       </c>
       <c r="N40">
-        <v>71790.755984546704</v>
+        <v>6515560.0043890597</v>
       </c>
       <c r="O40">
-        <v>1838.1115866405701</v>
+        <v>73723.257438978893</v>
       </c>
       <c r="P40">
+        <v>6283581.5563787399</v>
+      </c>
+      <c r="Q40">
+        <v>0.118745973253538</v>
+      </c>
+      <c r="R40">
+        <v>10.120958207086399</v>
+      </c>
+      <c r="S40">
+        <v>73863.296931297999</v>
+      </c>
+      <c r="T40">
+        <v>2581.6896186206</v>
+      </c>
+      <c r="U40">
         <f t="shared" si="0"/>
         <v>130.6154522689163</v>
       </c>
-      <c r="Q40">
+      <c r="V40">
         <f t="shared" si="1"/>
-        <v>111.25269801177855</v>
-      </c>
-      <c r="R40">
+        <v>114.39259242883382</v>
+      </c>
+      <c r="W40">
         <f t="shared" si="2"/>
-        <v>85.175755302463799</v>
+        <v>87.579677933754567</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2034</v>
       </c>
@@ -9424,49 +11180,64 @@
         <v>1.2149278239999901</v>
       </c>
       <c r="F41">
+        <v>1.2333358210000001</v>
+      </c>
+      <c r="G41">
         <v>1.2482463779999999</v>
       </c>
-      <c r="G41">
-        <v>0.69794956398321095</v>
-      </c>
       <c r="H41">
+        <v>0.718718541358213</v>
+      </c>
+      <c r="I41">
         <v>9.29055704173142E-3</v>
       </c>
-      <c r="I41">
-        <v>2.5700601341285899E-2</v>
-      </c>
       <c r="J41">
-        <v>1.3244162675742801</v>
+        <v>3.3906014053778001E-2</v>
       </c>
       <c r="K41">
-        <v>73698.696748731105</v>
+        <v>1.3603043661377301</v>
       </c>
       <c r="L41">
-        <v>71830.504075241406</v>
+        <v>85.188465253239102</v>
       </c>
       <c r="M41">
-        <v>0.115239563503098</v>
+        <v>75890.209500555095</v>
       </c>
       <c r="N41">
-        <v>71804.595924219597</v>
+        <v>6464970.47509907</v>
       </c>
       <c r="O41">
-        <v>1894.1008245114599</v>
+        <v>73218.942179816906</v>
       </c>
       <c r="P41">
+        <v>6237409.3117642496</v>
+      </c>
+      <c r="Q41">
+        <v>0.11746707120588</v>
+      </c>
+      <c r="R41">
+        <v>10.0068395138219</v>
+      </c>
+      <c r="S41">
+        <v>73317.074990685098</v>
+      </c>
+      <c r="T41">
+        <v>2573.1345098699799</v>
+      </c>
+      <c r="U41">
         <f t="shared" si="0"/>
         <v>131.13428217856426</v>
       </c>
-      <c r="Q41">
+      <c r="V41">
         <f t="shared" si="1"/>
-        <v>111.24439224909619</v>
-      </c>
-      <c r="R41">
+        <v>113.54665477882158</v>
+      </c>
+      <c r="W41">
         <f t="shared" si="2"/>
-        <v>84.832425511443148</v>
+        <v>86.58807818401462</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2035</v>
       </c>
@@ -9483,49 +11254,64 @@
         <v>1.223432318</v>
       </c>
       <c r="F42">
+        <v>1.2419691719999999</v>
+      </c>
+      <c r="G42">
         <v>1.2619770889999999</v>
       </c>
-      <c r="G42">
-        <v>0.70224070138956596</v>
-      </c>
       <c r="H42">
+        <v>0.718582120552826</v>
+      </c>
+      <c r="I42">
         <v>4.64527852086571E-3</v>
       </c>
-      <c r="I42">
-        <v>2.6352282904573601E-2</v>
-      </c>
       <c r="J42">
-        <v>1.34723431359444</v>
+        <v>3.3130423189720003E-2</v>
       </c>
       <c r="K42">
-        <v>73697.707347292206</v>
+        <v>1.3766007478260101</v>
       </c>
       <c r="L42">
-        <v>71758.349957732498</v>
+        <v>85.151029007410401</v>
       </c>
       <c r="M42">
-        <v>0.11466831980797999</v>
+        <v>75413.756387778005</v>
       </c>
       <c r="N42">
-        <v>71755.604513857907</v>
+        <v>6421558.95773347</v>
       </c>
       <c r="O42">
-        <v>1942.10283343432</v>
+        <v>72842.877826329801</v>
       </c>
       <c r="P42">
+        <v>6202646.0027730605</v>
+      </c>
+      <c r="Q42">
+        <v>0.116401372317552</v>
+      </c>
+      <c r="R42">
+        <v>9.9116966307142693</v>
+      </c>
+      <c r="S42">
+        <v>72915.266724324494</v>
+      </c>
+      <c r="T42">
+        <v>2498.4896634535398</v>
+      </c>
+      <c r="U42">
         <f t="shared" si="0"/>
         <v>131.65517314542257</v>
       </c>
-      <c r="Q42">
+      <c r="V42">
         <f t="shared" si="1"/>
-        <v>111.13264667451215</v>
-      </c>
-      <c r="R42">
+        <v>112.92437157243998</v>
+      </c>
+      <c r="W42">
         <f t="shared" si="2"/>
-        <v>84.411910310397133</v>
+        <v>85.772832828761636</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2036</v>
       </c>
@@ -9542,52 +11328,67 @@
         <v>1.231996345</v>
       </c>
       <c r="F43">
+        <v>1.250662956</v>
+      </c>
+      <c r="G43">
         <v>1.2758588360000001</v>
       </c>
-      <c r="G43">
-        <v>0.70607590566901501</v>
-      </c>
       <c r="H43">
+        <v>0.71919947173883103</v>
+      </c>
+      <c r="I43">
         <v>0</v>
       </c>
-      <c r="I43">
-        <v>2.7082132290445499E-2</v>
-      </c>
       <c r="J43">
-        <v>1.3697056892894599</v>
+        <v>3.2324779120007703E-2</v>
       </c>
       <c r="K43">
-        <v>73640.192229529799</v>
+        <v>1.39394173150578</v>
       </c>
       <c r="L43">
-        <v>71627.606961482394</v>
+        <v>85.119492339868799</v>
       </c>
       <c r="M43">
-        <v>0.114024691365603</v>
+        <v>75010.347303944902</v>
       </c>
       <c r="N43">
-        <v>71645.858801675902</v>
+        <v>6384842.6827490404</v>
       </c>
       <c r="O43">
-        <v>1994.3334278539601</v>
+        <v>72521.374337719302</v>
       </c>
       <c r="P43">
+        <v>6172982.56741626</v>
+      </c>
+      <c r="Q43">
+        <v>0.11544748843437599</v>
+      </c>
+      <c r="R43">
+        <v>9.8268316074470299</v>
+      </c>
+      <c r="S43">
+        <v>72585.654395629797</v>
+      </c>
+      <c r="T43">
+        <v>2424.6929083150899</v>
+      </c>
+      <c r="U43">
         <f t="shared" si="0"/>
         <v>132.15709091303094</v>
       </c>
-      <c r="Q43">
+      <c r="V43">
         <f t="shared" si="1"/>
-        <v>110.93016410327148</v>
-      </c>
-      <c r="R43">
+        <v>112.41389870780516</v>
+      </c>
+      <c r="W43">
         <f t="shared" si="2"/>
-        <v>83.938109818315894</v>
-      </c>
-      <c r="T43" t="s">
+        <v>85.060815073314345</v>
+      </c>
+      <c r="Y43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2037</v>
       </c>
@@ -9604,49 +11405,64 @@
         <v>1.240620319</v>
       </c>
       <c r="F44">
+        <v>1.2594175970000001</v>
+      </c>
+      <c r="G44">
         <v>1.2898932839999999</v>
       </c>
-      <c r="G44">
-        <v>0.710033093493183</v>
-      </c>
       <c r="H44">
+        <v>0.72097956152764797</v>
+      </c>
+      <c r="I44">
         <v>0</v>
       </c>
-      <c r="I44">
-        <v>2.8129745152489099E-2</v>
-      </c>
       <c r="J44">
-        <v>1.3913050951294399</v>
+        <v>3.2210332863553202E-2</v>
       </c>
       <c r="K44">
-        <v>73561.307032192693</v>
+        <v>1.41162338041476</v>
       </c>
       <c r="L44">
-        <v>71447.950606554194</v>
+        <v>85.093301238008493</v>
       </c>
       <c r="M44">
-        <v>0.113324101679037</v>
+        <v>74694.203553825893</v>
       </c>
       <c r="N44">
-        <v>71492.046212293106</v>
+        <v>6355976.3637388302</v>
       </c>
       <c r="O44">
-        <v>2069.2608198995899</v>
+        <v>72209.8143866194</v>
       </c>
       <c r="P44">
+        <v>6144571.48794128</v>
+      </c>
+      <c r="Q44">
+        <v>0.114532499229208</v>
+      </c>
+      <c r="R44">
+        <v>9.7459484584529701</v>
+      </c>
+      <c r="S44">
+        <v>72288.278394379202</v>
+      </c>
+      <c r="T44">
+        <v>2405.92515944673</v>
+      </c>
+      <c r="U44">
         <f t="shared" si="0"/>
         <v>132.64058383277808</v>
       </c>
-      <c r="Q44">
+      <c r="V44">
         <f t="shared" si="1"/>
-        <v>110.65192907937771</v>
-      </c>
-      <c r="R44">
+        <v>111.95335046365062</v>
+      </c>
+      <c r="W44">
         <f t="shared" si="2"/>
-        <v>83.42237788916718</v>
+        <v>84.403541682832042</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2038</v>
       </c>
@@ -9663,49 +11479,64 @@
         <v>1.249304661</v>
       </c>
       <c r="F45">
+        <v>1.2682335199999999</v>
+      </c>
+      <c r="G45">
         <v>1.30408211</v>
       </c>
-      <c r="G45">
-        <v>0.71341140662142499</v>
-      </c>
       <c r="H45">
+        <v>0.72269422102260195</v>
+      </c>
+      <c r="I45">
         <v>0</v>
       </c>
-      <c r="I45">
-        <v>2.8779892348246201E-2</v>
-      </c>
       <c r="J45">
-        <v>1.4125359573602101</v>
+        <v>3.1934364432237697E-2</v>
       </c>
       <c r="K45">
-        <v>73390.877554644394</v>
+        <v>1.4298278117635499</v>
       </c>
       <c r="L45">
-        <v>71232.869334308503</v>
+        <v>85.072031232417899</v>
       </c>
       <c r="M45">
-        <v>0.112586722560863</v>
+        <v>74344.277210815999</v>
       </c>
       <c r="N45">
-        <v>71278.695999278396</v>
+        <v>6324618.6728300797</v>
       </c>
       <c r="O45">
-        <v>2112.1815553659799</v>
+        <v>71898.452919464995</v>
       </c>
       <c r="P45">
+        <v>6116547.4323272603</v>
+      </c>
+      <c r="Q45">
+        <v>0.11363870706104399</v>
+      </c>
+      <c r="R45">
+        <v>9.6674756363087404</v>
+      </c>
+      <c r="S45">
+        <v>71970.139968914504</v>
+      </c>
+      <c r="T45">
+        <v>2374.1372419015001</v>
+      </c>
+      <c r="U45">
         <f t="shared" si="0"/>
         <v>133.10739848380834</v>
       </c>
-      <c r="Q45">
+      <c r="V45">
         <f t="shared" si="1"/>
-        <v>110.31883124408937</v>
-      </c>
-      <c r="R45">
+        <v>111.46064731131253</v>
+      </c>
+      <c r="W45">
         <f t="shared" si="2"/>
-        <v>82.879563796379756</v>
+        <v>83.737379425134662</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2039</v>
       </c>
@@ -9722,49 +11553,64 @@
         <v>1.2580497939999999</v>
       </c>
       <c r="F46">
+        <v>1.277111154</v>
+      </c>
+      <c r="G46">
         <v>1.318427013</v>
       </c>
-      <c r="G46">
-        <v>0.71653101118153395</v>
-      </c>
       <c r="H46">
+        <v>0.72453067273642102</v>
+      </c>
+      <c r="I46">
         <v>0</v>
       </c>
-      <c r="I46">
-        <v>2.9355192885087901E-2</v>
-      </c>
       <c r="J46">
-        <v>1.43345264496608</v>
+        <v>3.1829269950718102E-2</v>
       </c>
       <c r="K46">
-        <v>73192.002705167804</v>
+        <v>1.4483821657635101</v>
       </c>
       <c r="L46">
-        <v>70989.752697937904</v>
+        <v>85.055506577126494</v>
       </c>
       <c r="M46">
-        <v>0.111824739835794</v>
+        <v>74007.185566661705</v>
       </c>
       <c r="N46">
-        <v>71043.437348111707</v>
+        <v>6294718.65871982</v>
       </c>
       <c r="O46">
-        <v>2148.5653570560798</v>
+        <v>71577.432067082394</v>
       </c>
       <c r="P46">
+        <v>6088054.7439555498</v>
+      </c>
+      <c r="Q46">
+        <v>0.11275046629720401</v>
+      </c>
+      <c r="R46">
+        <v>9.5900480277159392</v>
+      </c>
+      <c r="S46">
+        <v>71651.590878967603</v>
+      </c>
+      <c r="T46">
+        <v>2355.5946876941698</v>
+      </c>
+      <c r="U46">
         <f t="shared" si="0"/>
         <v>133.55701394789875</v>
       </c>
-      <c r="Q46">
+      <c r="V46">
         <f t="shared" si="1"/>
-        <v>109.94231484890491</v>
-      </c>
-      <c r="R46">
+        <v>110.96730816008611</v>
+      </c>
+      <c r="W46">
         <f t="shared" si="2"/>
-        <v>82.318638010126492</v>
+        <v>83.086095503284469</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2040</v>
       </c>
@@ -9781,51 +11627,74 @@
         <v>1.266856142</v>
       </c>
       <c r="F47">
+        <v>1.286050932</v>
+      </c>
+      <c r="G47">
         <v>1.3329297099999999</v>
       </c>
-      <c r="G47">
-        <v>0.71935391321216602</v>
-      </c>
       <c r="H47">
+        <v>0.72632581038106603</v>
+      </c>
+      <c r="I47">
         <v>0</v>
       </c>
-      <c r="I47">
-        <v>2.9813818209167401E-2</v>
-      </c>
       <c r="J47">
-        <v>1.45416261100852</v>
+        <v>3.1790681237199699E-2</v>
       </c>
       <c r="K47">
-        <v>72957.802629568701</v>
+        <v>1.4672201272368099</v>
       </c>
       <c r="L47">
-        <v>70724.721823155007</v>
+        <v>85.042778165112196</v>
       </c>
       <c r="M47">
-        <v>0.11104717461001801</v>
+        <v>73662.511037226999</v>
       </c>
       <c r="N47">
-        <v>70782.651965030396</v>
+        <v>6264464.5852240203</v>
       </c>
       <c r="O47">
-        <v>2175.1506645382801</v>
+        <v>71245.804083346506</v>
       </c>
       <c r="P47">
+        <v>6058941.1118550804</v>
+      </c>
+      <c r="Q47">
+        <v>0.11186534273061401</v>
+      </c>
+      <c r="R47">
+        <v>9.5133395262038594</v>
+      </c>
+      <c r="S47">
+        <v>71320.729629710797</v>
+      </c>
+      <c r="T47">
+        <v>2341.78140751619</v>
+      </c>
+      <c r="U47">
         <f t="shared" si="0"/>
         <v>133.99008681877748</v>
       </c>
-      <c r="Q47">
+      <c r="V47">
         <f t="shared" si="1"/>
-        <v>109.53185972302153</v>
-      </c>
-      <c r="R47">
+        <v>110.45490108364689</v>
+      </c>
+      <c r="W47">
         <f t="shared" si="2"/>
-        <v>81.746241325422915</v>
+        <v>82.435129124916457</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="T48" t="s">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="Y48" t="s">
         <v>20</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="25:25" x14ac:dyDescent="0.25">
+      <c r="Y69" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -9876,27 +11745,27 @@
       </c>
       <c r="B2" s="2">
         <f>VLOOKUP($A2,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>63.151313047102896</v>
+        <v>95.899999999999991</v>
       </c>
       <c r="C2" s="2">
         <f>VLOOKUP($A2,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>3.1353135313531304</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
         <f>VLOOKUP($A2,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>93.293718169999991</v>
+        <v>3.1353135313531304</v>
       </c>
       <c r="E2" s="3">
         <f>VLOOKUP($A2,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>6666</v>
+        <v>9.3293718169999998E-2</v>
       </c>
       <c r="F2" s="3">
         <f>VLOOKUP($A2,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6457</v>
+        <v>785254.8</v>
       </c>
       <c r="G2" s="3">
         <f>VLOOKUP($A2,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>209</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9905,27 +11774,27 @@
       </c>
       <c r="B3" s="2">
         <f>VLOOKUP($A3,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>62.385896324709002</v>
+        <v>97.3</v>
       </c>
       <c r="C3" s="2">
         <f>VLOOKUP($A3,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>4.7295300029559497</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <f>VLOOKUP($A3,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>95.895196510000005</v>
+        <v>4.7295300029559497</v>
       </c>
       <c r="E3" s="3">
         <f>VLOOKUP($A3,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>6766</v>
+        <v>9.5895196510000003E-2</v>
       </c>
       <c r="F3" s="3">
         <f>VLOOKUP($A3,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6446</v>
+        <v>774707</v>
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP($A3,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>320</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9934,27 +11803,27 @@
       </c>
       <c r="B4" s="2">
         <f>VLOOKUP($A4,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>60.328172195161699</v>
+        <v>95.199999999999989</v>
       </c>
       <c r="C4" s="2">
         <f>VLOOKUP($A4,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>4.43542324462486</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <f>VLOOKUP($A4,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>93.375111910000001</v>
+        <v>4.43542324462486</v>
       </c>
       <c r="E4" s="3">
         <f>VLOOKUP($A4,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>6651</v>
+        <v>9.3375111910000003E-2</v>
       </c>
       <c r="F4" s="3">
         <f>VLOOKUP($A4,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6356</v>
+        <v>742916.70000000007</v>
       </c>
       <c r="G4" s="3">
         <f>VLOOKUP($A4,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>295</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9963,27 +11832,27 @@
       </c>
       <c r="B5" s="2">
         <f>VLOOKUP($A5,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>59.611339816995304</v>
+        <v>94.8</v>
       </c>
       <c r="C5" s="2">
         <f>VLOOKUP($A5,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>5.0361881785283398</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <f>VLOOKUP($A5,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>91.988950279999898</v>
+        <v>5.0361881785283398</v>
       </c>
       <c r="E5" s="3">
         <f>VLOOKUP($A5,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>6632</v>
+        <v>9.1988950279999912E-2</v>
       </c>
       <c r="F5" s="3">
         <f>VLOOKUP($A5,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6298</v>
+        <v>720235.20000000007</v>
       </c>
       <c r="G5" s="3">
         <f>VLOOKUP($A5,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>334</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9992,27 +11861,27 @@
       </c>
       <c r="B6" s="2">
         <f>VLOOKUP($A6,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>59.573052298395801</v>
+        <v>98.2</v>
       </c>
       <c r="C6" s="2">
         <f>VLOOKUP($A6,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>3.3660377358490501</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
         <f>VLOOKUP($A6,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>92.703461180000005</v>
+        <v>3.3660377358490501</v>
       </c>
       <c r="E6" s="3">
         <f>VLOOKUP($A6,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>6625</v>
+        <v>9.2703461180000002E-2</v>
       </c>
       <c r="F6" s="3">
         <f>VLOOKUP($A6,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6402</v>
+        <v>708212.5</v>
       </c>
       <c r="G6" s="3">
         <f>VLOOKUP($A6,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>223</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -10021,27 +11890,27 @@
       </c>
       <c r="B7" s="2">
         <f>VLOOKUP($A7,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>62.116384973990598</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2">
         <f>VLOOKUP($A7,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>2.7818023761228599</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
         <f>VLOOKUP($A7,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>100</v>
+        <v>2.7818023761228599</v>
       </c>
       <c r="E7" s="3">
         <f>VLOOKUP($A7,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>6902</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="3">
         <f>VLOOKUP($A7,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6710</v>
+        <v>690200</v>
       </c>
       <c r="G7" s="3">
         <f>VLOOKUP($A7,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>192</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10050,27 +11919,27 @@
       </c>
       <c r="B8" s="2">
         <f>VLOOKUP($A8,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>63.888204763338095</v>
+        <v>111.9</v>
       </c>
       <c r="C8" s="2">
         <f>VLOOKUP($A8,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>2.5128498001142199</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
         <f>VLOOKUP($A8,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>110.51107979999999</v>
+        <v>2.5128498001142199</v>
       </c>
       <c r="E8" s="3">
         <f>VLOOKUP($A8,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>7004</v>
+        <v>0.11051107979999999</v>
       </c>
       <c r="F8" s="3">
         <f>VLOOKUP($A8,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>6828</v>
+        <v>689841.6521040001</v>
       </c>
       <c r="G8" s="3">
         <f>VLOOKUP($A8,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>176</v>
+        <v>6828</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -10079,27 +11948,27 @@
       </c>
       <c r="B9" s="2">
         <f>VLOOKUP($A9,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>67.617640454346898</v>
+        <v>119.48013159999999</v>
       </c>
       <c r="C9" s="2">
         <f>VLOOKUP($A9,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>2.22818530597283</v>
+        <v>2.7871671125194197</v>
       </c>
       <c r="D9" s="2">
         <f>VLOOKUP($A9,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>123.04216708983699</v>
+        <v>1.7484126022216901</v>
       </c>
       <c r="E9" s="3">
         <f>VLOOKUP($A9,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>7283.6189322544496</v>
+        <v>0.12905356238150401</v>
       </c>
       <c r="F9" s="3">
         <f>VLOOKUP($A9,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>7121.3264054629099</v>
+        <v>666625.03964738303</v>
       </c>
       <c r="G9" s="3">
         <f>VLOOKUP($A9,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>162.29252679154899</v>
+        <v>7658.9128430508399</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10108,27 +11977,27 @@
       </c>
       <c r="B10" s="2">
         <f>VLOOKUP($A10,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>70.224070138956591</v>
+        <v>126.19770889999999</v>
       </c>
       <c r="C10" s="2">
         <f>VLOOKUP($A10,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>2.6352282904573601</v>
+        <v>0.46452785208657099</v>
       </c>
       <c r="D10" s="2">
         <f>VLOOKUP($A10,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>134.72343135944399</v>
+        <v>3.3130423189720002</v>
       </c>
       <c r="E10" s="3">
         <f>VLOOKUP($A10,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>7369.7707347292207</v>
+        <v>0.13766007478260101</v>
       </c>
       <c r="F10" s="3">
         <f>VLOOKUP($A10,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>7175.5604513857907</v>
+        <v>642155.895773347</v>
       </c>
       <c r="G10" s="3">
         <f>VLOOKUP($A10,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>194.21028334343202</v>
+        <v>7284.2877826329805</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -10137,27 +12006,27 @@
       </c>
       <c r="B11" s="2">
         <f>VLOOKUP($A11,labour_force_simulation!$A$1:$O$47,7)*100</f>
-        <v>71.935391321216599</v>
+        <v>133.29297099999999</v>
       </c>
       <c r="C11" s="2">
         <f>VLOOKUP($A11,labour_force_simulation!$A$1:$O$47,9)*100</f>
-        <v>2.9813818209167402</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
         <f>VLOOKUP($A11,labour_force_simulation!$A$1:$O$47,10)*100</f>
-        <v>145.41626110085198</v>
+        <v>3.1790681237199698</v>
       </c>
       <c r="E11" s="3">
         <f>VLOOKUP($A11,labour_force_simulation!$A$1:$O$47,11)*0.1</f>
-        <v>7295.7802629568705</v>
+        <v>0.14672201272368099</v>
       </c>
       <c r="F11" s="3">
         <f>VLOOKUP($A11,labour_force_simulation!$A$1:$O$47,14)*0.1</f>
-        <v>7078.26519650304</v>
+        <v>626446.4585224021</v>
       </c>
       <c r="G11" s="3">
         <f>VLOOKUP($A11,labour_force_simulation!$A$1:$O$47,15)*0.1</f>
-        <v>217.51506645382801</v>
+        <v>7124.5804083346511</v>
       </c>
     </row>
   </sheetData>
